--- a/processed_ruby_restored_xlsx/sc238_凛Ａ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc238_凛Ａ：遊園地.ss.xlsx
@@ -834,8 +834,8 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Does she realize anew that it's just the two of us and
-feel happy...？</t>
+          <t>Does she realize anew that it's just the two of us
+and feel happy...？</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1017,8 +1017,8 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... Rin-chan, you don't have to pull so hard—the
-ride isn't going to run away...！」</t>
+          <t>「Ahaha... Rin-chan, you don't have to pull so
+hard—the ride isn't going to run away...！」</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1263,8 +1263,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>While I was staring at the wagon, Rin-chan had already
-started moving briskly.</t>
+          <t>While I was staring at the wagon, Rin-chan had
+already started moving briskly.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1599,7 +1599,8 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan peers up at my face with a disappointed look.</t>
+          <t>Rin-chan peers up at my face with a disappointed
+look.</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1629,8 +1630,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>「...If you buy that much now, it'll be a pain to carry
-and we won't be able to play, right...？」</t>
+          <t>「...If you buy that much now, it'll be a pain to
+carry and we won't be able to play, right...？」</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1811,7 +1812,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, if it's just one, it's fine—anything you want.」</t>
+          <t>「Yeah, if it's just one, it's fine—anything you
+want.」</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2206,8 +2208,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan seemed unable to say anything and just stared
-hard at my face.</t>
+          <t>Rin-chan seemed unable to say anything and just
+stared hard at my face.</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2452,8 +2454,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>The small theater was sparsely populated, but it was a
-place I’d secretly been looking forward to.</t>
+          <t>The small theater was sparsely populated, but it was
+a place I’d secretly been looking forward to.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2468,8 +2470,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Believe it or not, they were showing a special episode
-of Pure Girl exclusive to this park.</t>
+          <t>Believe it or not, they were showing a special
+episode of Pure Girl exclusive to this park.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2823,8 +2825,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>『We won't let the Wrinkle-Wrinkle Gang attack the good
-children playing at the amusement park！』</t>
+          <t>『We won't let the Wrinkle-Wrinkle Gang attack the
+good children playing at the amusement park！』</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2993,8 +2995,8 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>At the same time, the smell of alcohol rubs across the
-tip of my nose.</t>
+          <t>At the same time, the smell of alcohol rubs across
+the tip of my nose.</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3195,7 +3197,8 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>And once you hear that lisping, you can guess already.</t>
+          <t>And once you hear that lisping, you can guess
+already.</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3287,8 +3290,8 @@
       <c r="B185" s="1" t="inlineStr">
         <is>
           <t>And the middle finger and the ring finger, and then
-the ring finger and the little finger, one finger at a
-time is being added.</t>
+the ring finger and the little finger, one finger at
+a time is being added.</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3606,8 +3609,8 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, even though she says she's just watching the
-movie, keeps staring intently at my profile.</t>
+          <t>Rin-chan, even though she says she's just watching
+the movie, keeps staring intently at my profile.</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3669,8 +3672,8 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>「...Ah, no, more importantly, this is a movie theater,
-so we have to be quiet, okay...？」</t>
+          <t>「...Ah, no, more importantly, this is a movie
+theater, so we have to be quiet, okay...？」</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3715,7 +3718,8 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>...Hmm, that doesn't sound like 'I understand' at all.</t>
+          <t>...Hmm, that doesn't sound like 'I understand' at
+all.</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4051,8 +4055,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>While I think that, her tiny little hands leave me and
-move downwards.</t>
+          <t>While I think that, her tiny little hands leave me
+and move downwards.</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4067,8 +4071,8 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>As I follow that mischievous little hand with my eyes,
-I somehow can tell where it's headed.</t>
+          <t>As I follow that mischievous little hand with my
+eyes, I somehow can tell where it's headed.</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4509,8 +4513,8 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>Because I'd been thinking about it so much earlier, it
-felt even more like real magic.</t>
+          <t>Because I'd been thinking about it so much earlier,
+it felt even more like real magic.</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4693,8 +4697,9 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Trying to hold back the sudden, jittering tremor in my
-hips, I end up spreading my legs without meaning to.</t>
+          <t>Trying to hold back the sudden, jittering tremor in
+my hips, I end up spreading my legs without meaning
+to.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4891,8 +4896,8 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan grabbed my penis over my clothes and squeezed
-it tight—gyuu~.</t>
+          <t>Rin-chan grabbed my penis over my clothes and
+squeezed it tight—gyuu~.</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4937,9 +4942,9 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>The unexpected, strong stimulation made a sound escape
-me before I could help it, and I hurriedly clamped my
-lips shut.</t>
+          <t>The unexpected, strong stimulation made a sound
+escape me before I could help it, and I hurriedly
+clamped my lips shut.</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -5120,8 +5125,8 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>She pokes at my penis with her finger and smiles at me
-suggestively.</t>
+          <t>She pokes at my penis with her finger and smiles at
+me suggestively.</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5583,8 +5588,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>…Apparently my dick had become a lot less controllable
-than I’d expected.</t>
+          <t>…Apparently my dick had become a lot less
+controllable than I’d expected.</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5599,8 +5604,8 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>The juice of my restraint was overflowing, wetting the
-head.</t>
+          <t>The juice of my restraint was overflowing, wetting
+the head.</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5767,8 +5772,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>My body was obedient to a startling degree; I couldn’t
-help but react.</t>
+          <t>My body was obedient to a startling degree; I
+couldn’t help but react.</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5860,8 +5865,8 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s tormenting hand grew more intense, matching
-the sounds I made.</t>
+          <t>Rin-chan’s tormenting hand grew more intense,
+matching the sounds I made.</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5876,8 +5881,8 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought she’d squeezed the base tight, she
-slowly, deliberately stroked upward.</t>
+          <t>Just when I thought she’d squeezed the base tight,
+she slowly, deliberately stroked upward.</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6326,8 +6331,8 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>She's really trying to make me release the white stuff
-here… trying to make me cum…！</t>
+          <t>She's really trying to make me release the white
+stuff here… trying to make me cum…！</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6357,8 +6362,8 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「Niini's gonna… come… nfu！ I'm gonna let out the white
-stuff…！」</t>
+          <t>「Niini's gonna… come… nfu！ I'm gonna let out the
+white stuff…！」</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6736,8 +6741,8 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan beams, smiling with a mischievous, very happy
-expression.</t>
+          <t>Rin-chan beams, smiling with a mischievous, very
+happy expression.</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6891,8 +6896,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>I shouldn't be thinking that if Rin-chan cleaned me up
-with her mouth…</t>
+          <t>I shouldn't be thinking that if Rin-chan cleaned me
+up with her mouth…</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -6952,8 +6957,8 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>「N-no no no no！ N-not… not thinking…？ I'm not thinking
-about anything…！」</t>
+          <t>「N-no no no no！ N-not… not thinking…？ I'm not
+thinking about anything…！」</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -7075,7 +7080,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>「I'll do what Niini is thinking right now... okay...？」</t>
+          <t>「I'll do what Niini is thinking right now...
+okay...？」</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7152,8 +7158,8 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan pressed her face against my crotch and stared
-up at me from below, just intently watching.</t>
+          <t>Rin-chan pressed her face against my crotch and
+stared up at me from below, just intently watching.</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -7243,8 +7249,8 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>When I thought that, I felt less resistance than I had
-just a moment ago.</t>
+          <t>When I thought that, I felt less resistance than I
+had just a moment ago.</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7335,8 +7341,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>Suddenly having my shaft taken into my mouth, I almost
-let out a sound without meaning to.</t>
+          <t>Suddenly having my shaft taken into my mouth, I
+almost let out a sound without meaning to.</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7582,8 +7588,8 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>When I couldn't help but speak up, she answered with a
-blank, puzzled look.</t>
+          <t>When I couldn't help but speak up, she answered with
+a blank, puzzled look.</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7781,8 +7787,8 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>「Umm...more, please stimulate my penis...torment it, I
-guess...！」</t>
+          <t>「Umm...more, please stimulate my penis...torment it,
+I guess...！」</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -8772,9 +8778,9 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>She licks with her tongue and lightly presses with her
-lips, but it's not the motion of trying to make me
-cum.</t>
+          <t>She licks with her tongue and lightly presses with
+her lips, but it's not the motion of trying to make
+me cum.</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -9036,8 +9042,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>Even if I tense my penis, that's not enough to make me
-come...！</t>
+          <t>Even if I tense my penis, that's not enough to make
+me come...！</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9387,8 +9393,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's mouth is so hot it makes my penis feel like
-it's burning...！</t>
+          <t>Rin-chan's mouth is so hot it makes my penis feel
+like it's burning...！</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9664,8 +9670,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>「Niini... such a nice mo... nchu, chuuuu... chu, chuu！
-Nn... fu！」</t>
+          <t>「Niini... such a nice mo... nchu, chuuuu... chu,
+chuu！  Nn... fu！」</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9898,7 +9904,8 @@
       <c r="B616" s="1" t="inlineStr">
         <is>
           <t>Even when I try to sink deeper into the chair, my
-sensations are numbed and I can't find any steadiness.</t>
+sensations are numbed and I can't find any
+steadiness.</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -10035,8 +10042,8 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>「puu... haa！ Your penis is all trembly...！ Niini, hold
-it, hold it... okay？」</t>
+          <t>「puu... haa！ Your penis is all trembly...！ Niini,
+hold it, hold it... okay？」</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10051,8 +10058,8 @@
       </c>
       <c r="B626" s="1" t="inlineStr">
         <is>
-          <t>Even if she tells me to hold it, there's nothing I can
-do.</t>
+          <t>Even if she tells me to hold it, there's nothing I
+can do.</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -10266,8 +10273,8 @@
       </c>
       <c r="B640" s="1" t="inlineStr">
         <is>
-          <t>On top of that, when she really sucks the inside of me
-up, I just can't stand it...！</t>
+          <t>On top of that, when she really sucks the inside of
+me up, I just can't stand it...！</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -10407,8 +10414,8 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan seems to be saying something while rubbing my
-penis with the inside of her cheek.</t>
+          <t>Rin-chan seems to be saying something while rubbing
+my penis with the inside of her cheek.</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10530,8 +10537,9 @@
       </c>
       <c r="B657" s="1" t="inlineStr">
         <is>
-          <t>She's rubbing mercilessly, and the penis I thought was
-already fully erect just keeps swelling even more.</t>
+          <t>She's rubbing mercilessly, and the penis I thought
+was already fully erect just keeps swelling even
+more.</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -10638,8 +10646,8 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>She acts like she just thought of it on a whim, but to
-me it's like a finishing blow...！</t>
+          <t>She acts like she just thought of it on a whim, but
+to me it's like a finishing blow...！</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -11498,8 +11506,8 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>Having been teased enough to be extra sensitive, I end
-up ejaculating even more than before！</t>
+          <t>Having been teased enough to be extra sensitive, I
+end up ejaculating even more than before！</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -11590,8 +11598,8 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>It's still coming out, and she keeps attacking me like
-she doesn't care...！</t>
+          <t>It's still coming out, and she keeps attacking me
+like she doesn't care...！</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -11758,8 +11766,8 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan smiles as if even that is fun, and savors the
-semen...</t>
+          <t>Rin-chan smiles as if even that is fun, and savors
+the semen...</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -11974,8 +11982,8 @@
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t>But it's hard for me even to move my body, and there's
-nothing I can do anymore......</t>
+          <t>But it's hard for me even to move my body, and
+there's nothing I can do anymore......</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -12438,8 +12446,8 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>They'd never suspect for a second that we'd been doing
-something naughty.</t>
+          <t>They'd never suspect for a second that we'd been
+doing something naughty.</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12559,7 +12567,8 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>「I think one more day wouldn't have hurt... would it？」</t>
+          <t>「I think one more day wouldn't have hurt... would
+it？」</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -13351,8 +13360,9 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>Because she ate an amount of whiskey bonbons I'd never
-seen before, Rin-chan's memory was completely gone.</t>
+          <t>Because she ate an amount of whiskey bonbons I'd
+never seen before, Rin-chan's memory was completely
+gone.</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13383,8 +13393,8 @@
       </c>
       <c r="B843" s="1" t="inlineStr">
         <is>
-          <t>So I'm using up the best of my energy today to try and
-soothe her…</t>
+          <t>So I'm using up the best of my energy today to try
+and soothe her…</t>
         </is>
       </c>
       <c r="C843" t="n">

--- a/processed_ruby_restored_xlsx/sc238_凛Ａ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc238_凛Ａ：遊園地.ss.xlsx
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh...! Hah!？」</t>
+          <t>Nnngh...! Hah!？</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>「Lick！ Ah—this is...！？」</t>
+          <t>Lick！ Ah—this is...！？</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>「That's not really true, but...」</t>
+          <t>That's not really true, but...</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -4759,8 +4759,8 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaah！ D-don't say such lewd things in a place like
-this... okay...？」</t>
+          <t>Uwaaah！ D-don't say such lewd things in a place like
+this... okay...？</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu？ Pervert-san, are you lewd...？」</t>
+          <t>Nnnu？ Pervert-san, are you lewd...？</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>「Niinii？ Is your penis a pervert？」</t>
+          <t>「Nii-nii？ Is your penis a pervert？」</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！」</t>
+          <t>Ugh！</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5279,8 +5279,8 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>I thought I was somehow resisting, but this hits me
-far harder than I expected.</t>
+          <t>She thought she was somehow resisting, but this hits
+her far harder than she expected.</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>As proof, my penis is throbbing violently, nearly
+          <t>As proof, his penis is throbbing violently, nearly
 bursting out of her panties.</t>
         </is>
       </c>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>In that moment, Rin-chan had exposed my penis.</t>
+          <t>In that moment, Rin-chan had exposed her penis.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5541,8 +5541,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>「Mmm...？ There's some liquid leaking from the tip...
-Did you wet yourself？」</t>
+          <t>Mmm...？ There's some liquid leaking from the tip...
+Did you wet yourself？</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -6096,8 +6096,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>「Uwaa...！ Not there... it really hurts there...
-ahh...」</t>
+          <t>Uwaa...！ Not there... it really hurts there... ahh...</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6331,7 +6330,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>She's really trying to make me release the white
+          <t>They're really trying to make me release the white
 stuff here… trying to make me cum…！</t>
         </is>
       </c>
@@ -6362,7 +6361,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「Niini's gonna… come… nfu！ I'm gonna let out the
+          <t>「Niini's gonna… come… nfu！ He's gonna let out the
 white stuff…！」</t>
         </is>
       </c>
@@ -6680,7 +6679,7 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaaaah, ah... ah」</t>
+          <t>Fuwaaaah, ah... ah</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -7189,7 +7188,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>「Nn fufuu... I'll make it all nice... okay？」</t>
+          <t>Nn fufuu... I'll make it all nice... okay？</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7295,8 +7294,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>「Mmm...lero...chu！ Nnnh, Niini's taste...
-hapu...chuu...」</t>
+          <t>Mmm...lero...chu！ Nnnh, Niini's taste...
+hapu...chuu...</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -8138,7 +8137,7 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnffuu！ Fuhi！ Fuhihii...！」</t>
+          <t>Nn... nnffuu！ Fuhi！ Fuhihii...！</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8505,8 +8504,8 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... you little rascal...！ Behave yourself a
-liiittle bit...！」</t>
+          <t>Nngh... you little rascal...！ Behave yourself a
+liiittle bit...！</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8888,7 +8887,7 @@
       <c r="B550" s="1" t="inlineStr">
         <is>
           <t>It's fine — I still want to get to the point of
-cumming...！</t>
+cumming...！"</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9226,7 +9225,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>Finally... she's going to make me come...！？</t>
+          <t>Finally... she's going to make me come...！？"</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -11201,7 +11200,7 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Slurp, licky... lick！ Hehe！」</t>
+          <t>Smooch！ Slurp, licky... lick！ Hehe！</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -11262,8 +11261,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Lick, lick, lick, lick！ Nnnh！ Lick, lick,
-leru—！」</t>
+          <t>Smooch！ Lick, lick, lick, lick！ Nnnh！ Lick, lick,
+leru—！</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11690,7 +11689,7 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>「U-uh！　Ah...！　Fuwaaaaaa...！！」</t>
+          <t>U-uh！　Ah...！　Fuwaaaaaa...！！</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -11735,7 +11734,7 @@
       </c>
       <c r="B735" s="1" t="inlineStr">
         <is>
-          <t>「Nn~...！ Nf—！ Nfufu... Nnnu！」</t>
+          <t>Nn~...！ Nf—！ Nfufu... Nnnu！</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -13360,7 +13359,7 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>Because she ate an amount of whiskey bonbons I'd
+          <t>Because she ate an amount of whiskey bonbons he'd
 never seen before, Rin-chan's memory was completely
 gone.</t>
         </is>
